--- a/国服服务器列表.xlsx
+++ b/国服服务器列表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B298B4B-8013-4C7B-9184-CBD04A0EE9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B375BDD-EABC-4537-BA9C-EB969E89F479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{8B27E1A9-18C2-4F7A-9B32-BAFDEA5E4F5B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="78">
   <si>
     <t>艾欧尼亚</t>
   </si>
@@ -231,27 +231,6 @@
     <t>HN10</t>
   </si>
   <si>
-    <t>WT1_NEW</t>
-  </si>
-  <si>
-    <t>WT2_NEW</t>
-  </si>
-  <si>
-    <t>WT3_NEW</t>
-  </si>
-  <si>
-    <t>WT4_NEW</t>
-  </si>
-  <si>
-    <t>WT5</t>
-  </si>
-  <si>
-    <t>WT6</t>
-  </si>
-  <si>
-    <t>WT7</t>
-  </si>
-  <si>
     <t>BGP2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -301,6 +280,14 @@
   </si>
   <si>
     <t>比赛服（Tournament）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TJ100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TJ101</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -676,16 +663,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -741,7 +728,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -811,7 +798,7 @@
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -853,7 +840,7 @@
         <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -867,7 +854,7 @@
         <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -951,12 +938,12 @@
         <v>37</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
         <v>38</v>
@@ -965,12 +952,12 @@
         <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
@@ -979,12 +966,12 @@
         <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
         <v>42</v>
@@ -993,12 +980,12 @@
         <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
         <v>44</v>
@@ -1007,12 +994,12 @@
         <v>45</v>
       </c>
       <c r="D24" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
         <v>46</v>
@@ -1021,12 +1008,12 @@
         <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
         <v>48</v>
@@ -1035,12 +1022,12 @@
         <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
         <v>50</v>
@@ -1049,12 +1036,12 @@
         <v>51</v>
       </c>
       <c r="D27" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
         <v>52</v>
@@ -1068,7 +1055,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
         <v>54</v>
@@ -1082,7 +1069,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B30" t="s">
         <v>56</v>
@@ -1091,21 +1078,21 @@
         <v>57</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/国服服务器列表.xlsx
+++ b/国服服务器列表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B375BDD-EABC-4537-BA9C-EB969E89F479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDD8C18-E1C8-4FC7-9CBD-9A5393D3539C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{8B27E1A9-18C2-4F7A-9B32-BAFDEA5E4F5B}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$32</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="82">
   <si>
     <t>艾欧尼亚</t>
   </si>
@@ -288,6 +288,22 @@
   </si>
   <si>
     <t>TJ101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>试炼之地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PBE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PREPBE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>试炼之地 临时过渡服务器</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -652,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEC4D7EB-5F6A-4227-9205-BFADD3F1FF57}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.25" bestFit="1" customWidth="1"/>
@@ -943,30 +959,24 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -974,10 +984,10 @@
         <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s">
         <v>76</v>
@@ -988,10 +998,10 @@
         <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s">
         <v>77</v>
@@ -1002,13 +1012,13 @@
         <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -1016,13 +1026,13 @@
         <v>66</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -1030,10 +1040,10 @@
         <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
         <v>77</v>
@@ -1041,62 +1051,90 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D29" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D30" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>75</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B33" t="s">
         <v>73</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C33" t="s">
         <v>74</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D33" t="s">
         <v>72</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D30" xr:uid="{CEC4D7EB-5F6A-4227-9205-BFADD3F1FF57}"/>
+  <autoFilter ref="A1:D32" xr:uid="{CEC4D7EB-5F6A-4227-9205-BFADD3F1FF57}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
